--- a/branches/feature-s3-annotation-ig/ValueSet-vs-senologie-therapie-status.xlsx
+++ b/branches/feature-s3-annotation-ig/ValueSet-vs-senologie-therapie-status.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -109,12 +110,6 @@
     <t>Laufend</t>
   </si>
   <si>
-    <t>therapie-abgeschlossen</t>
-  </si>
-  <si>
-    <t>Abgeschlossen</t>
-  </si>
-  <si>
     <t>therapie-abgebrochen</t>
   </si>
   <si>
@@ -125,6 +120,15 @@
   </si>
   <si>
     <t>https://www.senologie.org/fhir/CodeSystem/form-helper</t>
+  </si>
+  <si>
+    <t>182992009</t>
+  </si>
+  <si>
+    <t>Abgeschlossen (Treatment completed)</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
   </si>
   <si>
     <t>Level</t>
@@ -412,7 +416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -445,26 +449,18 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -474,38 +470,84 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -523,17 +565,17 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>13</v>
@@ -544,17 +586,17 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>13</v>
